--- a/reports/sheets/contract_specialist_v32_and_sorter_v14_deck.xlsx
+++ b/reports/sheets/contract_specialist_v32_and_sorter_v14_deck.xlsx
@@ -20,9 +20,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11. SORTER v14 · headlines" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12. SORTER v14 · failures" sheetId="12" state="visible" r:id="rId12"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13. SORTER v14 · per-subtype" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. CODEBOOK · SORTER · subtype" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. CODEBOOK · SORTER · rules" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. DOCCLASS v5 · bonus + sourc" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14. PART B · SORTER · qwen line" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15. PART B · SORTER · qwen all " sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="16. PART B · SORTER · llama run" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="17. CODEBOOK · SORTER · subtype" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="18. CODEBOOK · SORTER · rules" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19. DOCCLASS v5 · bonus + sourc" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -668,7 +671,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 1/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 1/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -918,7 +921,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 10/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 10/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1235,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 11/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 11/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1517,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 12/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 12/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -2125,7 +2128,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 13/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 13/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -2142,6 +2145,1596 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="2" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PART B · SORTER  ·  Qwen lineage summary v3→v13</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>qwen3.7-flash × sorter prompt lineage — best full-surface run per version (max n, then max strict)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Version</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Reference run</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Strict</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v3</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v3</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>0.8359</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>0.9846</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>early lineage baseline (50/195-doc surfaces)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v4</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v4</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>195</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>0.8103</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>0.9795</t>
+        </is>
+      </c>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v5</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v5</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>509</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>0.8585</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>0.9843</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>first full-509 run</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v6</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v6</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>509</v>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>0.9312</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>0.9436 @195 (ab200 arm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v7</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v7</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>243</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>0.8765</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>0.9918</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>+0.82pp @250 (KANBAN-003)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v8</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v8</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>509</v>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>0.9018</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>0.9921</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>+2.06pp @243 (promotion cluster fixed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v9</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v9</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>509</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>0.9175</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>former aggregate champion (KANBAN-012)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v10</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v10</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>243</v>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>0.9342</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>0.9918</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>marketing title-wins — logic repair (KANBAN-013)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v11</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v11</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>243</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>0.9342</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>0.9918</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>affiliate-is-not-marketing — logic repair (KANBAN-013)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v12</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v12</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>509</v>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>0.9293</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>strategic_alliance title-wins — logic repair (KANBAN-023)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v13</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v13</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>509</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>0.9430</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>AGGREGATE CHAMPION — maintenance title-wins (KANBAN-031)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>The 509-doc surfaces are the only directly comparable ones (same seed 42): v5 0.8585 → v6 0.9312 → v8 0.9018 → v9 0.9175 → v12 0.9293 → v13 0.9430. 243-doc runs (v7/v10/v11) are a different surface — never compare across surfaces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 14/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B16:O16"/>
+    <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="2" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PART B · SORTER  ·  Qwen lineage — all 30 runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>all 30 qwen3.7-flash sorter_v3→v13 subtype runs in the experiment log, chronological (both v13 qwen rows: the degraded first run and the clean champion rerun)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C4" s="15" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="inlineStr">
+        <is>
+          <t>Strict</t>
+        </is>
+      </c>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="I4" s="15" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K4" s="15" t="inlineStr">
+        <is>
+          <t>Strict</t>
+        </is>
+      </c>
+      <c r="L4" s="15" t="inlineStr">
+        <is>
+          <t>Exact</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>08-10 04:24</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v3_subtype</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>0.8400</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="inlineStr">
+        <is>
+          <t>0.9600</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>08-13 05:12</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v9_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="K5" s="12" t="inlineStr">
+        <is>
+          <t>0.8872</t>
+        </is>
+      </c>
+      <c r="L5" s="18" t="inlineStr">
+        <is>
+          <t>0.9949</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>08-10 04:33</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v3_subtype</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>0.8400</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>0.9600</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>08-13 05:25</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v8_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>509</v>
+      </c>
+      <c r="K6" s="16" t="inlineStr">
+        <is>
+          <t>0.9018</t>
+        </is>
+      </c>
+      <c r="L6" s="18" t="inlineStr">
+        <is>
+          <t>0.9921</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>08-10 04:51</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v3_subtype</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>0.8359</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>0.9846</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>08-13 05:38</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v9_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J7" s="12" t="n">
+        <v>509</v>
+      </c>
+      <c r="K7" s="12" t="inlineStr">
+        <is>
+          <t>0.9116</t>
+        </is>
+      </c>
+      <c r="L7" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>08-10 05:15</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v3_subtype</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
+        <v>195</v>
+      </c>
+      <c r="E8" s="16" t="inlineStr">
+        <is>
+          <t>0.7897</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>0.9744</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>08-15 19:34</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v9_subtype_langfuse_rerun</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>243</v>
+      </c>
+      <c r="K8" s="16" t="inlineStr">
+        <is>
+          <t>0.9300</t>
+        </is>
+      </c>
+      <c r="L8" s="18" t="inlineStr">
+        <is>
+          <t>0.9918</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>08-10 05:15</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v4_subtype</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>0.8103</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>0.9795</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>08-15 19:34</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v10_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="n">
+        <v>243</v>
+      </c>
+      <c r="K9" s="12" t="inlineStr">
+        <is>
+          <t>0.9342</t>
+        </is>
+      </c>
+      <c r="L9" s="18" t="inlineStr">
+        <is>
+          <t>0.9918</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>08-11 00:47</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v5_subtype</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
+        <v>509</v>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>0.8585</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>0.9843</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>08-15 19:40</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v11_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="n">
+        <v>243</v>
+      </c>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>0.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>08-11 01:06</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>pilot_langfuse_sorter_v5</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>08-15 19:47</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v11_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>243</v>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
+        <is>
+          <t>0.9342</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>0.9918</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>08-11 01:14</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v5_subtype_ab200</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
+        <v>195</v>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>0.8410</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>0.9846</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>08-15 20:29</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>pilot_nobt_sorter_v11</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="L12" s="18" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>08-11 01:19</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v6_subtype_ab200</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>0.9385</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="inlineStr">
+        <is>
+          <t>08-15 21:23</t>
+        </is>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v12_subtype_langfuse_pilot</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>08-11 01:23</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v6_subtype_langfuse_ab200</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
+        <v>195</v>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>0.9436</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>08-15 21:54</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v9_subtype_langfuse_rerun_509</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="n">
+        <v>509</v>
+      </c>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t>0.9143</t>
+        </is>
+      </c>
+      <c r="L14" s="18" t="inlineStr">
+        <is>
+          <t>0.9957</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>08-11 01:52</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v6_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>509</v>
+      </c>
+      <c r="E15" s="12" t="inlineStr">
+        <is>
+          <t>0.9312</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+      <c r="H15" s="12" t="inlineStr">
+        <is>
+          <t>08-15 22:19</t>
+        </is>
+      </c>
+      <c r="I15" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v12_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>509</v>
+      </c>
+      <c r="K15" s="12" t="inlineStr">
+        <is>
+          <t>0.9234</t>
+        </is>
+      </c>
+      <c r="L15" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>08-13 04:25</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v6_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>243</v>
+      </c>
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>0.8683</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>0.9918</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>08-15 22:36</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v9_subtype_langfuse_rerun_509_clean</t>
+        </is>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>509</v>
+      </c>
+      <c r="K16" s="16" t="inlineStr">
+        <is>
+          <t>0.9175</t>
+        </is>
+      </c>
+      <c r="L16" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>08-13 04:31</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v7_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>243</v>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>0.8765</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>0.9918</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="inlineStr">
+        <is>
+          <t>08-16 03:27</t>
+        </is>
+      </c>
+      <c r="I17" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v12_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>509</v>
+      </c>
+      <c r="K17" s="12" t="inlineStr">
+        <is>
+          <t>0.9293</t>
+        </is>
+      </c>
+      <c r="L17" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>08-13 04:48</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v8_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n">
+        <v>243</v>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>0.8971</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>0.9877</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>08-16 03:39</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>sorter_v13_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="n">
+        <v>509</v>
+      </c>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>0.7741</t>
+        </is>
+      </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>0.8134</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>08-13 05:00</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v9_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>243</v>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>0.9259</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>0.9918</t>
+        </is>
+      </c>
+      <c r="H19" s="12" t="inlineStr">
+        <is>
+          <t>08-16 03:56</t>
+        </is>
+      </c>
+      <c r="I19" s="12" t="inlineStr">
+        <is>
+          <t>sorter_v13_subtype_langfuse</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="n">
+        <v>509</v>
+      </c>
+      <c r="K19" s="12" t="inlineStr">
+        <is>
+          <t>0.9430</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Surfaces: n=509 (full corpus, seed 42) · n=243 (stratified) · n=195 (stratified) · n=50 · pilots (n=5/10/1). Only same-surface runs are comparable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 15/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B20:O20"/>
+    <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="2" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="46" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PART B · SORTER  ·  Llama runs (Langfuse)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>the ONLY llama run recorded anywhere: llama-4-scout × contracts_specialist_v31 EXTRACTION in Langfuse llm-dojo — there are NO llama sorter-task runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Run identity (fetched from Langfuse llm-dojo, 2026-08-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>llama-4-scout_contracts_specialist_v31_extraction_langfuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>Task / prompt</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>contract_entity_extraction · contracts_specialist_v31</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>llama-4-scout (OpenRouter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Traces / scored</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>509 doc traces · only 20 scored (run truncated)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>2026-08-16 06:55-07:22 UTC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Langfuse llm-dojo traces + scores (sourced via langfuse-cli; NOT in reports/experiment_log.jsonl)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Headline scores (n=20 scored docs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Llama-4-scout (n=20)</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Qwen 3.7-Flash v31 (n=509)</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>Qwen 3.7-Flash v32 (n=509)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Overall extraction score</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>0.6627</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>0.8737</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>0.8807</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Field presence</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>0.8935</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>0.9655</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="inlineStr">
+        <is>
+          <t>0.9701</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Schema valid</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E15" s="18" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Verified precision</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>0.9589</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>0.9799</t>
+        </is>
+      </c>
+      <c r="E16" s="18" t="inlineStr">
+        <is>
+          <t>0.9799</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Category presence</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>0.4782</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>0.8474</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>0.8555</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Tokens (619 generations incl. chunk windows)</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>10,337,518 total</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Cost recorded</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>0 (no Langfuse price for the model — OpenRouter-billed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Searched before building: reports/experiment_log.jsonl (0 hits), Langfuse llm-dojo (model/session 'llama' filters → this session only), Braintrust (experiment reads 403 Forbidden), LangSmith (LANGSMITH_PROJECT=HEARSAY only). If llama SORTER runs exist, they live outside this repo's reach — point me at them and I'll fold them in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 16/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A11:P11"/>
+    <mergeCell ref="B21:O21"/>
+    <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A18:P18"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A2:P2"/>
+  </mergeCells>
+  <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2800,7 +4393,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 14/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 17/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -2817,7 +4410,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3057,7 +4650,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 15/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 18/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -3076,7 +4669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3509,7 +5102,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 16/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 19/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -3595,40 +5188,47 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Part B — Sorter v14 (contract-subtype classification, n=509)</t>
+          <t>Part B — Sorter (contract-subtype classification, n=509)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>•  11 · Run metadata &amp; headlines (+ v13 A/B note) · 12 · Failure modes &amp; examples · 13 · Per-subtype accuracy</t>
+          <t>•  11 · Sorter v14 run metadata &amp; headlines (+ v13 A/B note) · 12 · Failure modes &amp; examples · 13 · Per-subtype accuracy</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>•  14 · Codebook: 25 CUAD subtypes · 15 · Codebook: equivalence families, failure modes, scoring rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+          <t>•  14 · Qwen lineage summary v3→v13 · 15 · Qwen lineage — all 30 runs · 16 · Llama runs (Langfuse)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>•  17 · Codebook: 25 CUAD subtypes · 18 · Codebook: equivalence families, failure modes, scoring rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Part C — Docclass + sources</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="B14" s="9" t="inlineStr">
-        <is>
-          <t>•  16 · Docclass v5 diag-30 bonus slide + sources &amp; navigation</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>•  19 · Docclass v5 diag-30 bonus slide + sources &amp; navigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Same-surface comparisons only: the 509-doc runs are the full corpus (seed 42); the docclass slide is a 30-doc diagnostic, not comparable to 509-doc numbers.</t>
         </is>
@@ -3637,15 +5237,15 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 2/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 2/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B17:O17"/>
+    <mergeCell ref="B18:O18"/>
     <mergeCell ref="A36:P36"/>
-    <mergeCell ref="A13:P13"/>
+    <mergeCell ref="A14:P14"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A9:P9"/>
     <mergeCell ref="A4:P4"/>
@@ -3996,7 +5596,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 3/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 3/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -4276,7 +5876,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 4/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 4/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -4573,7 +6173,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 5/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 5/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -4919,7 +6519,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 6/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 6/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -5137,7 +6737,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 7/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 7/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -5472,7 +7072,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 8/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 8/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>
@@ -5768,7 +7368,7 @@
     <row r="36" ht="16" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 9/16 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
+          <t>contract_specialist_v32_and_sorter_v14_deck.xlsx · slide 9/19 · generated 2026-08-16 · source: reports/experiment_log.jsonl</t>
         </is>
       </c>
     </row>

--- a/reports/sheets/contract_specialist_v32_and_sorter_v14_deck.xlsx
+++ b/reports/sheets/contract_specialist_v32_and_sorter_v14_deck.xlsx
@@ -3452,263 +3452,403 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>the ONLY llama run recorded anywhere: llama-4-scout × contracts_specialist_v31 EXTRACTION in Langfuse llm-dojo — there are NO llama sorter-task runs</t>
+          <t>llama sorter run landed 2026-08-16 (KANBAN-042): meta-llama/llama-3.3-70b-instruct × sorter_v13, full-509; plus the earlier llama-4-scout EXTRACTION run from Langfuse</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Run identity (fetched from Langfuse llm-dojo, 2026-08-16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="B5" s="11" t="inlineStr">
+          <t>Llama sorter run — meta-llama/llama-3.3-70b-instruct × sorter_v13 (full-509, KANBAN-042)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Llama-3.3-70B (n=509)</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>Qwen champion (n=509)</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (n=509)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Subtype accuracy</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>0.8782</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>0.9430</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>0.9528</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>Exact match (doc_type + subtype)</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>0.9941</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>0.9961</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Subtype equiv</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>0.8998</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>0.9470</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>0.9548</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Mean confidence</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>0.9424</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>0.9583</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="inlineStr">
+        <is>
+          <t>0.9555</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Failed rows</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>29</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>95% CI [0.8487, 0.9057] — 62 fails: 47 family_confusion / 11 equivalent_family / 3 function_over_form / 1 other_fallback. 6.66M tokens, est. cost None (OpenRouter-billed, no local price).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Earlier llama run — llama-4-scout × contracts_specialist_v31 EXTRACTION (Langfuse llm-dojo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Session</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>llama-4-scout_contracts_specialist_v31_extraction_langfuse</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="B6" s="11" t="inlineStr">
+    <row r="15" ht="24" customHeight="1">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Task / prompt</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>contract_entity_extraction · contracts_specialist_v31</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="B7" s="11" t="inlineStr">
+    <row r="16" ht="24" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>llama-4-scout (OpenRouter)</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="B8" s="11" t="inlineStr">
+    <row r="17" ht="24" customHeight="1">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>Traces / scored</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>509 doc traces · only 20 scored (run truncated)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="B9" s="11" t="inlineStr">
+    <row r="18" ht="24" customHeight="1">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>Window</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>2026-08-16 06:55-07:22 UTC</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>Provenance</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>Langfuse llm-dojo traces + scores (sourced via langfuse-cli; NOT in reports/experiment_log.jsonl)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Headline scores (n=20 scored docs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Llama-4-scout (n=20)</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>Qwen 3.7-Flash v31 (n=509)</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="inlineStr">
-        <is>
-          <t>Qwen 3.7-Flash v32 (n=509)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>Overall extraction score</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>0.6627</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>0.8737</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>0.8807</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>Field presence</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>0.8935</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>0.9655</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>0.9701</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>Schema valid</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>1.0000</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>Verified precision</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>0.9589</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>0.9799</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>0.9799</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Category presence</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>0.4782</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>0.8474</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>0.8555</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>Usage</t>
         </is>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
         <is>
+          <t>Provenance</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>Langfuse llm-dojo traces + scores (sourced via langfuse-cli; NOT in reports/experiment_log.jsonl)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>llama-4-scout extraction headline scores (n=20 scored docs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Llama-4-scout (n=20)</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>Qwen 3.7-Flash v31 (n=509)</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Qwen 3.7-Flash v32 (n=509)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>Overall extraction score</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>0.6627</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>0.8737</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>0.8807</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="B23" s="16" t="inlineStr">
+        <is>
+          <t>Field presence</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>0.8935</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>0.9655</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="inlineStr">
+        <is>
+          <t>0.9701</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Schema valid</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>1.0000</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Verified precision</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>0.9589</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>0.9799</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
+        <is>
+          <t>0.9799</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="B26" s="12" t="inlineStr">
+        <is>
+          <t>Category presence</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>0.4782</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>0.8474</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>0.8555</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Usage (llama-4-scout run)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="B28" s="11" t="inlineStr">
+        <is>
           <t>Tokens (619 generations incl. chunk windows)</t>
         </is>
       </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>10,337,518 total</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="B20" s="11" t="inlineStr">
+    <row r="29" ht="24" customHeight="1">
+      <c r="B29" s="11" t="inlineStr">
         <is>
           <t>Cost recorded</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>0 (no Langfuse price for the model — OpenRouter-billed)</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>Searched before building: reports/experiment_log.jsonl (0 hits), Langfuse llm-dojo (model/session 'llama' filters → this session only), Braintrust (experiment reads 403 Forbidden), LangSmith (LANGSMITH_PROJECT=HEARSAY only). If llama SORTER runs exist, they live outside this repo's reach — point me at them and I'll fold them in.</t>
+    <row r="30" ht="26" customHeight="1">
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Sweep status (sorter_v13, full-509): qwen3.7-flash 0.9430 · deepseek-v4-pro 0.9528 · deepseek-v4-flash 0.9253 · gpt-5-nano 0.8978 · llama-3.3-70b 0.8782 · gpt-4.1-nano pending. The llama-3.3-70b sorter run traces to Langfuse llm-dojo (KANBAN-042, research-funding key).</t>
         </is>
       </c>
     </row>
@@ -3720,13 +3860,15 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A11:P11"/>
-    <mergeCell ref="B21:O21"/>
+  <mergeCells count="9">
     <mergeCell ref="A36:P36"/>
+    <mergeCell ref="A13:P13"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A18:P18"/>
+    <mergeCell ref="B30:O30"/>
+    <mergeCell ref="A27:P27"/>
+    <mergeCell ref="B11:O11"/>
     <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A20:P20"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.3" top="0.3" bottom="0.3" header="0.5" footer="0.5"/>
